--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487868_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487868_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8319</v>
+        <v>3.9397</v>
       </c>
       <c r="E2" t="n">
-        <v>2.801</v>
+        <v>1.408</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0309</v>
+        <v>2.5318</v>
       </c>
       <c r="G2" t="n">
         <v>1.5088</v>
@@ -610,13 +610,13 @@
         <v>1.2487</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1805</v>
+        <v>1.2883</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1398</v>
+        <v>0.7468</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0407</v>
+        <v>0.5416</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1061</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5623</v>
+        <v>3.1884</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0911</v>
+        <v>1.8052</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4712</v>
+        <v>1.3831</v>
       </c>
       <c r="G3" t="n">
         <v>0.8783</v>
@@ -688,13 +688,13 @@
         <v>1.6649</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4759</v>
+        <v>1.1019</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8136</v>
+        <v>0.5276999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6623</v>
+        <v>0.5742</v>
       </c>
       <c r="V3" t="n">
         <v>0.5838</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6488</v>
+        <v>2.1724</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0079</v>
+        <v>-0.4968</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6409</v>
+        <v>2.6692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5496</v>
+        <v>-0.6287</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3219</v>
+        <v>-0.6247</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7723</v>
+        <v>-0.0041</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2069</v>
+        <v>-0.2449</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0893</v>
+        <v>-1.2369</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1176</v>
+        <v>0.9919</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6573</v>
+        <v>-0.3838</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2326</v>
+        <v>0.6122</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8899</v>
+        <v>-0.996</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8078</v>
+        <v>0.4286</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8416</v>
+        <v>-0.2519</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9663</v>
+        <v>0.6805</v>
       </c>
       <c r="V4" t="n">
         <v>0.7076</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4267</v>
+        <v>1.8252</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3409</v>
+        <v>1.9779</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0858</v>
+        <v>-0.1526</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4151</v>
+        <v>1.9572</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5479000000000001</v>
+        <v>-0.3067</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8672</v>
+        <v>2.2639</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0683</v>
+        <v>1.7533</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2746</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7937</v>
+        <v>2.3333</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3468</v>
+        <v>0.2039</v>
       </c>
       <c r="N5" t="n">
         <v>0.2733</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0735</v>
+        <v>-0.0694</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.7461</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R5" t="n">
         <v>0.4162</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2801</v>
+        <v>0.4924</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2051</v>
+        <v>0.0977</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0751</v>
+        <v>0.3948</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4776</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>1.1675</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2477</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3152</v>
+        <v>1.7122</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3541</v>
+        <v>0.3649</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6692</v>
+        <v>1.3473</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6287</v>
+        <v>0.5496</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6247</v>
+        <v>1.3219</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0041</v>
+        <v>-0.7723</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.2449</v>
+        <v>1.2069</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2369</v>
+        <v>1.0893</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9919</v>
+        <v>0.1176</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3838</v>
+        <v>-0.6573</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6122</v>
+        <v>0.2326</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.996</v>
+        <v>-0.8899</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6649</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4286</v>
+        <v>0.8713</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1091</v>
+        <v>0.1986</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6805</v>
+        <v>0.6727</v>
       </c>
       <c r="V6" t="n">
         <v>0.7076</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1926</v>
+        <v>0.3888</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2278</v>
+        <v>-1.0586</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0352</v>
+        <v>1.4475</v>
       </c>
       <c r="G7" t="n">
-        <v>1.9572</v>
+        <v>1.414</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.3067</v>
+        <v>1.2711</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2639</v>
+        <v>0.1429</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7533</v>
+        <v>1.0672</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5800999999999999</v>
+        <v>0.9978</v>
       </c>
       <c r="L7" t="n">
-        <v>2.3333</v>
+        <v>0.0694</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2039</v>
+        <v>0.3468</v>
       </c>
       <c r="N7" t="n">
         <v>0.2733</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0694</v>
+        <v>0.0735</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6244</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1402</v>
+        <v>1.1393</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6524</v>
+        <v>0.663</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5122</v>
+        <v>0.4763</v>
       </c>
       <c r="V7" t="n">
+        <v>-0.7076</v>
+      </c>
+      <c r="W7" t="n">
+        <v>-0.7076</v>
+      </c>
+      <c r="X7" t="n">
         <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.1675</v>
-      </c>
-      <c r="X7" t="n">
-        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,31 +1033,31 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.235</v>
+        <v>0.3463</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5944</v>
+        <v>-0.9449</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3594</v>
+        <v>1.2913</v>
       </c>
       <c r="G8" t="n">
-        <v>1.414</v>
+        <v>2.4151</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2711</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1429</v>
+        <v>1.8672</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0672</v>
+        <v>2.0683</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9978</v>
+        <v>0.2746</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0694</v>
+        <v>1.7937</v>
       </c>
       <c r="M8" t="n">
         <v>0.3468</v>
@@ -1069,31 +1069,31 @@
         <v>0.0735</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4568</v>
+        <v>-3.7461</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0812</v>
+        <v>-4.1624</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5154</v>
+        <v>1.1998</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1272</v>
+        <v>0.9192</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3882</v>
+        <v>0.2806</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.7076</v>
+        <v>0.4776</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.2477</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5731</v>
+        <v>-0.3048</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.6898</v>
+        <v>0.1675</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8834</v>
+        <v>-0.4723</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2811</v>
@@ -1156,13 +1156,13 @@
         <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0028</v>
+        <v>0.2655</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9134</v>
+        <v>-0.0562</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.3217</v>
       </c>
       <c r="V9" t="n">
         <v>1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2657</v>
+        <v>-1.6315</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.174</v>
+        <v>0.2546</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.0916</v>
+        <v>-1.8861</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9711</v>
@@ -1234,13 +1234,13 @@
         <v>1.4568</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5402</v>
+        <v>0.0939</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8482</v>
+        <v>-0.4195</v>
       </c>
       <c r="U10" t="n">
-        <v>0.308</v>
+        <v>0.5135</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2112</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2975</v>
+        <v>-3.0307</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4487</v>
+        <v>-4.27</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1513</v>
+        <v>1.2393</v>
       </c>
       <c r="G11" t="n">
         <v>0.4857</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5376</v>
+        <v>0.7292</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7177</v>
+        <v>0.461</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1801</v>
+        <v>0.2682</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7076</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.606200000000001</v>
+        <v>8.606000000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7923000000000009</v>
+        <v>-0.7921999999999993</v>
       </c>
       <c r="F12" t="n">
-        <v>9.398500000000002</v>
+        <v>9.398499999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>7.327799999999998</v>
+        <v>7.3278</v>
       </c>
       <c r="H12" t="n">
         <v>10.7363</v>
@@ -1390,13 +1390,13 @@
         <v>10.4058</v>
       </c>
       <c r="S12" t="n">
-        <v>7.610299999999998</v>
+        <v>7.6102</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8865</v>
+        <v>2.8864</v>
       </c>
       <c r="U12" t="n">
-        <v>4.723999999999999</v>
+        <v>4.7241</v>
       </c>
       <c r="V12" t="n">
         <v>-0.08839999999999981</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.5398</v>
+        <v>5.401</v>
       </c>
       <c r="E13" t="n">
-        <v>6.038</v>
+        <v>5.0736</v>
       </c>
       <c r="F13" t="n">
-        <v>1.5018</v>
+        <v>0.3274</v>
       </c>
       <c r="G13" t="n">
         <v>4.7393</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0721</v>
+        <v>-0.0667</v>
       </c>
       <c r="T13" t="n">
-        <v>0.512</v>
+        <v>-0.4524</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5601</v>
+        <v>0.3857</v>
       </c>
       <c r="V13" t="n">
         <v>-1.769</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7371</v>
+        <v>4.0014</v>
       </c>
       <c r="E14" t="n">
         <v>1.1994</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5377</v>
+        <v>2.802</v>
       </c>
       <c r="G14" t="n">
         <v>1.0996</v>
@@ -1546,13 +1546,13 @@
         <v>3.1218</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.8026</v>
+        <v>-1.5384</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7738</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0288</v>
+        <v>-0.7645</v>
       </c>
       <c r="V14" t="n">
         <v>4.4401</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3142</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.229</v>
+        <v>0.0925</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5432</v>
+        <v>0.7487</v>
       </c>
       <c r="G15" t="n">
         <v>0.1648</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5155</v>
+        <v>-0.9886</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6524</v>
+        <v>-0.331</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8631</v>
+        <v>-0.6576</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6735</v>
+        <v>-0.468</v>
       </c>
       <c r="E16" t="n">
         <v>-1.1081</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4345</v>
+        <v>0.6401</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4067</v>
@@ -1702,13 +1702,13 @@
         <v>1.0406</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3074</v>
+        <v>-1.1019</v>
       </c>
       <c r="T16" t="n">
         <v>-0.5872000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7202</v>
+        <v>-0.5147</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.1504</v>
+        <v>-0.5838</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3446</v>
+        <v>-1.1303</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1943</v>
+        <v>0.5466</v>
       </c>
       <c r="G17" t="n">
         <v>-3.0772</v>
@@ -1780,13 +1780,13 @@
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2376</v>
+        <v>-0.671</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5129</v>
+        <v>-0.2985</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7248</v>
+        <v>-0.3725</v>
       </c>
       <c r="V17" t="n">
         <v>1.2914</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.3254</v>
+        <v>-1.7261</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3808</v>
+        <v>-1.4879</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0554</v>
+        <v>-0.2382</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2759</v>
@@ -1858,13 +1858,13 @@
         <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2981</v>
+        <v>-0.6989</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1214</v>
+        <v>-0.2286</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1767</v>
+        <v>-0.4703</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.1401</v>
+        <v>-2.6527</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.6546</v>
+        <v>-4.226</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5146</v>
+        <v>1.5733</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5188</v>
@@ -1936,13 +1936,13 @@
         <v>2.9137</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9115</v>
+        <v>-1.4242</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3577</v>
+        <v>-0.9291</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5538</v>
+        <v>-0.4951</v>
       </c>
       <c r="V19" t="n">
         <v>-2.5827</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.2521</v>
+        <v>-2.8029</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.974</v>
+        <v>-0.7597</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2781</v>
+        <v>-2.0432</v>
       </c>
       <c r="G20" t="n">
         <v>-1.3619</v>
@@ -2014,13 +2014,13 @@
         <v>0.6244</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1202</v>
+        <v>-0.671</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8482</v>
+        <v>-0.6338</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.272</v>
+        <v>-0.0372</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3538</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7403</v>
+        <v>-3.7887</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7037</v>
+        <v>-1.8109</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.0366</v>
+        <v>-1.9779</v>
       </c>
       <c r="G21" t="n">
         <v>-4.425</v>
@@ -2092,13 +2092,13 @@
         <v>0.4162</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1416</v>
+        <v>0.0931</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2048</v>
+        <v>0.0977</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0633</v>
+        <v>-0.0045</v>
       </c>
       <c r="V21" t="n">
         <v>1.1675</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9155</v>
+        <v>-6.8274</v>
       </c>
       <c r="E22" t="n">
         <v>-5.2411</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6744</v>
+        <v>-1.5863</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2659</v>
@@ -2170,13 +2170,13 @@
         <v>1.2487</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6309</v>
+        <v>-0.5427999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-0.5872000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0437</v>
+        <v>0.0444</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1051</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.606199999999999</v>
+        <v>-8.606</v>
       </c>
       <c r="E23" t="n">
-        <v>-9.398500000000002</v>
+        <v>-9.3985</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7924000000000009</v>
+        <v>0.7925</v>
       </c>
       <c r="G23" t="n">
         <v>-7.3277</v>
@@ -2248,10 +2248,10 @@
         <v>16.6495</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.610099999999999</v>
+        <v>-7.6104</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.724</v>
+        <v>-4.7239</v>
       </c>
       <c r="U23" t="n">
         <v>-2.8863</v>
